--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>16.88417518319731</v>
+      </c>
+      <c r="C2">
         <v>16.73008112148617</v>
-      </c>
-      <c r="C2">
-        <v>16.88417518319731</v>
       </c>
       <c r="D2">
         <v>5.97725732910952</v>
       </c>
       <c r="E2">
-        <v>12.52117968859266</v>
+        <v>12.63650724866961</v>
       </c>
       <c r="F2">
         <v>74.84231306273774</v>
       </c>
       <c r="G2">
-        <v>12.63650724866961</v>
+        <v>12.52117968859266</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.21109339888989</v>
+      </c>
+      <c r="C3">
         <v>29.03566558472737</v>
-      </c>
-      <c r="C3">
-        <v>27.21109339888989</v>
       </c>
       <c r="D3">
         <v>3.444040216959915</v>
       </c>
       <c r="E3">
-        <v>18.58321143657886</v>
+        <v>17.4154610155741</v>
       </c>
       <c r="F3">
         <v>64.00132754784704</v>
       </c>
       <c r="G3">
-        <v>17.4154610155741</v>
+        <v>18.58321143657886</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>26.73274951593029</v>
+      </c>
+      <c r="C4">
         <v>28.33678049639148</v>
-      </c>
-      <c r="C4">
-        <v>26.73274951593029</v>
       </c>
       <c r="D4">
         <v>3.528982412548045</v>
       </c>
       <c r="E4">
-        <v>18.27359668539644</v>
+        <v>17.23920199784324</v>
       </c>
       <c r="F4">
         <v>64.48720131676032</v>
       </c>
       <c r="G4">
-        <v>17.23920199784324</v>
+        <v>18.27359668539644</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.77422102176638</v>
+      </c>
+      <c r="C5">
         <v>32.45489165480405</v>
-      </c>
-      <c r="C5">
-        <v>26.77422102176638</v>
       </c>
       <c r="D5">
         <v>3.081199625117151</v>
       </c>
       <c r="E5">
-        <v>20.38251115593863</v>
+        <v>16.81490311143713</v>
       </c>
       <c r="F5">
         <v>62.80258573262424</v>
       </c>
       <c r="G5">
-        <v>16.81490311143713</v>
+        <v>20.38251115593863</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.77240841777085</v>
+      </c>
+      <c r="C6">
         <v>31.44290724863601</v>
-      </c>
-      <c r="C6">
-        <v>28.77240841777085</v>
       </c>
       <c r="D6">
         <v>3.180367489852198</v>
       </c>
       <c r="E6">
-        <v>19.62540667092341</v>
+        <v>17.95858797774332</v>
       </c>
       <c r="F6">
         <v>62.41600535133327</v>
       </c>
       <c r="G6">
-        <v>17.95858797774332</v>
+        <v>19.62540667092341</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>22.51438252214732</v>
+      </c>
+      <c r="C7">
         <v>23.60674831468605</v>
-      </c>
-      <c r="C7">
-        <v>22.51438252214732</v>
       </c>
       <c r="D7">
         <v>4.236076848321746</v>
       </c>
       <c r="E7">
-        <v>16.15560198548327</v>
+        <v>15.40802647311023</v>
       </c>
       <c r="F7">
         <v>68.4363715414065</v>
       </c>
       <c r="G7">
-        <v>15.40802647311023</v>
+        <v>16.15560198548327</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>30.63743128818387</v>
+      </c>
+      <c r="C8">
         <v>22.17611661486166</v>
-      </c>
-      <c r="C8">
-        <v>30.63743128818387</v>
       </c>
       <c r="D8">
         <v>4.509355796451011</v>
       </c>
       <c r="E8">
-        <v>14.51187863849059</v>
+        <v>20.04889730563822</v>
       </c>
       <c r="F8">
         <v>65.43922405587118</v>
       </c>
       <c r="G8">
-        <v>20.04889730563822</v>
+        <v>14.51187863849059</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>23.35175829123105</v>
+      </c>
+      <c r="C9">
         <v>22.15496973638137</v>
-      </c>
-      <c r="C9">
-        <v>23.35175829123105</v>
       </c>
       <c r="D9">
         <v>4.513659968390156</v>
       </c>
       <c r="E9">
+        <v>16.04857631517881</v>
+      </c>
+      <c r="F9">
+        <v>68.72534442601395</v>
+      </c>
+      <c r="G9">
         <v>15.22607925880725</v>
-      </c>
-      <c r="F9">
-        <v>68.72534442601393</v>
-      </c>
-      <c r="G9">
-        <v>16.04857631517881</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.4</v>
+      </c>
+      <c r="C10">
         <v>31.60326530612245</v>
-      </c>
-      <c r="C10">
-        <v>24.4</v>
       </c>
       <c r="D10">
         <v>3.164229994317301</v>
       </c>
       <c r="E10">
-        <v>20.25807937039518</v>
+        <v>15.64069825853985</v>
       </c>
       <c r="F10">
         <v>64.10122237106498</v>
       </c>
       <c r="G10">
-        <v>15.64069825853985</v>
+        <v>20.25807937039518</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.65549123480045</v>
+      </c>
+      <c r="C11">
         <v>32.57671435406493</v>
-      </c>
-      <c r="C11">
-        <v>24.65549123480045</v>
       </c>
       <c r="D11">
         <v>3.069677282771214</v>
       </c>
       <c r="E11">
-        <v>20.71885605881998</v>
+        <v>15.6809421724136</v>
       </c>
       <c r="F11">
         <v>63.60020176876641</v>
       </c>
       <c r="G11">
-        <v>15.6809421724136</v>
+        <v>20.71885605881998</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.73547937459729</v>
+      </c>
+      <c r="C12">
         <v>32.70477467881705</v>
-      </c>
-      <c r="C12">
-        <v>27.73547937459729</v>
       </c>
       <c r="D12">
         <v>3.057657512765872</v>
       </c>
       <c r="E12">
-        <v>20.38439472174412</v>
+        <v>17.28710761412999</v>
       </c>
       <c r="F12">
         <v>62.3284976641259</v>
       </c>
       <c r="G12">
-        <v>17.28710761412999</v>
+        <v>20.38439472174412</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>31.40812497272767</v>
+      </c>
+      <c r="C13">
         <v>25.57926430161016</v>
-      </c>
-      <c r="C13">
-        <v>31.40812497272767</v>
       </c>
       <c r="D13">
         <v>3.909416581371545</v>
       </c>
       <c r="E13">
-        <v>16.29383380400703</v>
+        <v>20.0067821484957</v>
       </c>
       <c r="F13">
         <v>63.69938404749728</v>
       </c>
       <c r="G13">
-        <v>20.0067821484957</v>
+        <v>16.29383380400703</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>23.58072408779831</v>
+      </c>
+      <c r="C14">
         <v>36.77529165632424</v>
-      </c>
-      <c r="C14">
-        <v>23.58072408779831</v>
       </c>
       <c r="D14">
         <v>2.7192170475364</v>
       </c>
       <c r="E14">
-        <v>22.93352792888417</v>
+        <v>14.70523196674185</v>
       </c>
       <c r="F14">
         <v>62.36124010437398</v>
       </c>
       <c r="G14">
-        <v>14.70523196674185</v>
+        <v>22.93352792888417</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>20.04062138544382</v>
+      </c>
+      <c r="C15">
         <v>36.88964154671183</v>
-      </c>
-      <c r="C15">
-        <v>20.04062138544382</v>
       </c>
       <c r="D15">
         <v>2.710788064269319</v>
       </c>
       <c r="E15">
-        <v>23.50702844527828</v>
+        <v>12.77039941882198</v>
       </c>
       <c r="F15">
         <v>63.72257213589973</v>
       </c>
       <c r="G15">
-        <v>12.77039941882198</v>
+        <v>23.50702844527828</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>28.4677071399878</v>
+      </c>
+      <c r="C16">
         <v>21.72793953550653</v>
-      </c>
-      <c r="C16">
-        <v>28.4677071399878</v>
       </c>
       <c r="D16">
         <v>4.602369213913996</v>
       </c>
       <c r="E16">
-        <v>14.46642430486077</v>
+        <v>18.95374983903082</v>
       </c>
       <c r="F16">
         <v>66.57982585610841</v>
       </c>
       <c r="G16">
-        <v>18.95374983903082</v>
+        <v>14.46642430486077</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.27381749558653</v>
+      </c>
+      <c r="C17">
         <v>29.80002435015523</v>
-      </c>
-      <c r="C17">
-        <v>26.27381749558653</v>
       </c>
       <c r="D17">
         <v>3.355701955977734</v>
       </c>
       <c r="E17">
-        <v>19.09354187590807</v>
+        <v>16.83422230456447</v>
       </c>
       <c r="F17">
         <v>64.07223581952746</v>
       </c>
       <c r="G17">
-        <v>16.83422230456447</v>
+        <v>19.09354187590807</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.75408630009916</v>
+      </c>
+      <c r="C18">
         <v>31.53887982599239</v>
-      </c>
-      <c r="C18">
-        <v>25.75408630009916</v>
       </c>
       <c r="D18">
         <v>3.170689655172414</v>
       </c>
       <c r="E18">
-        <v>20.05104271522843</v>
+        <v>16.37332357217664</v>
       </c>
       <c r="F18">
-        <v>63.57563371259495</v>
+        <v>63.57563371259494</v>
       </c>
       <c r="G18">
-        <v>16.37332357217664</v>
+        <v>20.05104271522842</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>22.42804289208001</v>
+      </c>
+      <c r="C19">
         <v>32.59296419389226</v>
-      </c>
-      <c r="C19">
-        <v>22.42804289208001</v>
       </c>
       <c r="D19">
         <v>3.068146837001693</v>
       </c>
       <c r="E19">
-        <v>21.02486934291215</v>
+        <v>14.46774428425805</v>
       </c>
       <c r="F19">
         <v>64.5073863728298</v>
       </c>
       <c r="G19">
-        <v>14.46774428425805</v>
+        <v>21.02486934291215</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>25.73059133109163</v>
+      </c>
+      <c r="C20">
         <v>26.72213511219067</v>
-      </c>
-      <c r="C20">
-        <v>25.73059133109163</v>
       </c>
       <c r="D20">
         <v>3.742215941209723</v>
       </c>
       <c r="E20">
-        <v>17.52814510807206</v>
+        <v>16.87775084866344</v>
       </c>
       <c r="F20">
         <v>65.59410404326449</v>
       </c>
       <c r="G20">
-        <v>16.87775084866344</v>
+        <v>17.52814510807206</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>19.0664732241765</v>
+      </c>
+      <c r="C21">
         <v>31.80509001507994</v>
-      </c>
-      <c r="C21">
-        <v>19.0664732241765</v>
       </c>
       <c r="D21">
         <v>3.144150824682037</v>
       </c>
       <c r="E21">
-        <v>21.0809044012108</v>
+        <v>12.63755264067911</v>
       </c>
       <c r="F21">
         <v>66.28154295811011</v>
       </c>
       <c r="G21">
-        <v>12.63755264067911</v>
+        <v>21.0809044012108</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.20323332767166</v>
+      </c>
+      <c r="C22">
         <v>37.30679554684001</v>
-      </c>
-      <c r="C22">
-        <v>26.20323332767166</v>
       </c>
       <c r="D22">
         <v>2.680476801456893</v>
       </c>
       <c r="E22">
-        <v>22.81621243885395</v>
+        <v>16.02545942168584</v>
       </c>
       <c r="F22">
         <v>61.15832813946022</v>
       </c>
       <c r="G22">
-        <v>16.02545942168584</v>
+        <v>22.81621243885395</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.33133646127108</v>
+      </c>
+      <c r="C23">
         <v>25.80484978895969</v>
-      </c>
-      <c r="C23">
-        <v>26.33133646127108</v>
       </c>
       <c r="D23">
         <v>3.875240538806927</v>
       </c>
       <c r="E23">
+        <v>17.30774059102664</v>
+      </c>
+      <c r="F23">
+        <v>65.73058156954313</v>
+      </c>
+      <c r="G23">
         <v>16.96167783943023</v>
-      </c>
-      <c r="F23">
-        <v>65.73058156954312</v>
-      </c>
-      <c r="G23">
-        <v>17.30774059102664</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>14.83542709740319</v>
+      </c>
+      <c r="C24">
         <v>32.70537337382067</v>
-      </c>
-      <c r="C24">
-        <v>14.83542709740319</v>
       </c>
       <c r="D24">
         <v>3.057601540181344</v>
       </c>
       <c r="E24">
-        <v>22.16700280150607</v>
+        <v>10.05513529140481</v>
       </c>
       <c r="F24">
         <v>67.77786190708912</v>
       </c>
       <c r="G24">
-        <v>10.05513529140481</v>
+        <v>22.16700280150607</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>27.79506610219338</v>
+      </c>
+      <c r="C25">
         <v>23.78311094088761</v>
-      </c>
-      <c r="C25">
-        <v>27.79506610219338</v>
       </c>
       <c r="D25">
         <v>4.204664404440099</v>
       </c>
       <c r="E25">
-        <v>15.69032653963642</v>
+        <v>18.33711596511256</v>
       </c>
       <c r="F25">
         <v>65.97255749525102</v>
       </c>
       <c r="G25">
-        <v>18.33711596511256</v>
+        <v>15.69032653963642</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>28.32844863333825</v>
+      </c>
+      <c r="C26">
         <v>16.05274070325623</v>
-      </c>
-      <c r="C26">
-        <v>28.32844863333825</v>
       </c>
       <c r="D26">
         <v>6.22946584938704</v>
       </c>
       <c r="E26">
-        <v>11.11830479927176</v>
+        <v>19.62059515058877</v>
       </c>
       <c r="F26">
         <v>69.26110005013946</v>
       </c>
       <c r="G26">
-        <v>19.62059515058877</v>
+        <v>11.11830479927176</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>23.39690259823371</v>
+      </c>
+      <c r="C27">
         <v>27.50776677565363</v>
-      </c>
-      <c r="C27">
-        <v>23.39690259823371</v>
       </c>
       <c r="D27">
         <v>3.63533691468212</v>
       </c>
       <c r="E27">
-        <v>18.22857230978009</v>
+        <v>15.50442587052401</v>
       </c>
       <c r="F27">
         <v>66.26700181969589</v>
       </c>
       <c r="G27">
-        <v>15.50442587052401</v>
+        <v>18.22857230978009</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>25.39162773821942</v>
+      </c>
+      <c r="C28">
         <v>28.39584561658125</v>
-      </c>
-      <c r="C28">
-        <v>25.39162773821942</v>
       </c>
       <c r="D28">
         <v>3.521641910237981</v>
       </c>
       <c r="E28">
-        <v>18.46434237921943</v>
+        <v>16.51085565313814</v>
       </c>
       <c r="F28">
         <v>65.02480196764242</v>
       </c>
       <c r="G28">
-        <v>16.51085565313814</v>
+        <v>18.46434237921943</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>29.74333112701064</v>
+      </c>
+      <c r="C29">
         <v>25.52715352854036</v>
-      </c>
-      <c r="C29">
-        <v>29.74333112701064</v>
       </c>
       <c r="D29">
         <v>3.917397209532041</v>
       </c>
       <c r="E29">
-        <v>16.44044171380627</v>
+        <v>19.15581779305491</v>
       </c>
       <c r="F29">
         <v>64.40374049313883</v>
       </c>
       <c r="G29">
-        <v>19.15581779305491</v>
+        <v>16.44044171380627</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>24.31496062992126</v>
+      </c>
+      <c r="C30">
         <v>34.08976377952756</v>
-      </c>
-      <c r="C30">
-        <v>24.31496062992126</v>
       </c>
       <c r="D30">
         <v>2.933431884325773</v>
       </c>
       <c r="E30">
-        <v>21.52067364569974</v>
+        <v>15.34989610983527</v>
       </c>
       <c r="F30">
         <v>63.12943024446499</v>
       </c>
       <c r="G30">
-        <v>15.34989610983527</v>
+        <v>21.52067364569974</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>21.54067221985227</v>
+      </c>
+      <c r="C31">
         <v>24.82206605446911</v>
-      </c>
-      <c r="C31">
-        <v>21.54067221985227</v>
       </c>
       <c r="D31">
         <v>4.028673510922165</v>
       </c>
       <c r="E31">
-        <v>16.95927962754167</v>
+        <v>14.71731977265929</v>
       </c>
       <c r="F31">
         <v>68.32340059979904</v>
       </c>
       <c r="G31">
-        <v>14.71731977265929</v>
+        <v>16.95927962754167</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.25346703648389</v>
+      </c>
+      <c r="C32">
         <v>31.9376289026385</v>
-      </c>
-      <c r="C32">
-        <v>26.25346703648389</v>
       </c>
       <c r="D32">
         <v>3.131102822468407</v>
       </c>
       <c r="E32">
-        <v>20.18927090240859</v>
+        <v>16.59604599148056</v>
       </c>
       <c r="F32">
         <v>63.21468310611085</v>
       </c>
       <c r="G32">
-        <v>16.59604599148056</v>
+        <v>20.18927090240859</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>22.8296531873352</v>
+      </c>
+      <c r="C33">
         <v>39.76369235723919</v>
-      </c>
-      <c r="C33">
-        <v>22.8296531873352</v>
       </c>
       <c r="D33">
         <v>2.514856998228296</v>
       </c>
       <c r="E33">
-        <v>24.45591621481096</v>
+        <v>14.04095174428681</v>
       </c>
       <c r="F33">
         <v>61.50313204090222</v>
       </c>
       <c r="G33">
-        <v>14.04095174428681</v>
+        <v>24.45591621481096</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.77803219071992</v>
+      </c>
+      <c r="C34">
         <v>23.20883561182571</v>
-      </c>
-      <c r="C34">
-        <v>27.77803219071992</v>
       </c>
       <c r="D34">
         <v>4.308703877804473</v>
       </c>
       <c r="E34">
+        <v>18.39764781864796</v>
+      </c>
+      <c r="F34">
+        <v>66.23092554696602</v>
+      </c>
+      <c r="G34">
         <v>15.37142663438602</v>
-      </c>
-      <c r="F34">
-        <v>66.23092554696601</v>
-      </c>
-      <c r="G34">
-        <v>18.39764781864796</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>23.30875280538634</v>
+      </c>
+      <c r="C35">
         <v>25.59428388219667</v>
-      </c>
-      <c r="C35">
-        <v>23.30875280538634</v>
       </c>
       <c r="D35">
         <v>3.907122405153901</v>
       </c>
       <c r="E35">
-        <v>17.18855736696401</v>
+        <v>15.65364503229776</v>
       </c>
       <c r="F35">
         <v>67.15779760073823</v>
       </c>
       <c r="G35">
-        <v>15.65364503229776</v>
+        <v>17.18855736696401</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>26.05418984389019</v>
+      </c>
+      <c r="C36">
         <v>31.8858783420061</v>
-      </c>
-      <c r="C36">
-        <v>26.05418984389019</v>
       </c>
       <c r="D36">
         <v>3.13618458075408</v>
       </c>
       <c r="E36">
-        <v>20.18859350147694</v>
+        <v>16.49625085207908</v>
       </c>
       <c r="F36">
         <v>63.31515564644399</v>
       </c>
       <c r="G36">
-        <v>16.49625085207908</v>
+        <v>20.18859350147694</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>34.6868669993944</v>
+      </c>
+      <c r="C37">
         <v>16.553553156389</v>
-      </c>
-      <c r="C37">
-        <v>34.6868669993944</v>
       </c>
       <c r="D37">
         <v>6.040999116942096</v>
       </c>
       <c r="E37">
-        <v>10.9451911991108</v>
+        <v>22.93491843229846</v>
       </c>
       <c r="F37">
         <v>66.11989036859075</v>
       </c>
       <c r="G37">
-        <v>22.93491843229846</v>
+        <v>10.9451911991108</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>35.57561818779195</v>
+      </c>
+      <c r="C38">
         <v>15.19649157893233</v>
-      </c>
-      <c r="C38">
-        <v>35.57561818779195</v>
       </c>
       <c r="D38">
         <v>6.580466253055086</v>
       </c>
       <c r="E38">
-        <v>10.07911317447534</v>
+        <v>23.59562272016676</v>
       </c>
       <c r="F38">
         <v>66.32526410535792</v>
       </c>
       <c r="G38">
-        <v>23.59562272016676</v>
+        <v>10.07911317447534</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>31.00929614873838</v>
+      </c>
+      <c r="C39">
         <v>26.50232403718459</v>
-      </c>
-      <c r="C39">
-        <v>31.00929614873838</v>
       </c>
       <c r="D39">
         <v>3.773253993109928</v>
       </c>
       <c r="E39">
-        <v>16.82563102703272</v>
+        <v>19.68698951362175</v>
       </c>
       <c r="F39">
         <v>63.48737945934553</v>
       </c>
       <c r="G39">
-        <v>19.68698951362175</v>
+        <v>16.82563102703272</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>29.76650902264124</v>
+      </c>
+      <c r="C40">
         <v>23.39936600428819</v>
-      </c>
-      <c r="C40">
-        <v>29.76650902264124</v>
       </c>
       <c r="D40">
         <v>4.273620062256127</v>
       </c>
       <c r="E40">
-        <v>15.2771405511666</v>
+        <v>19.4341650954612</v>
       </c>
       <c r="F40">
         <v>65.28869435337221</v>
       </c>
       <c r="G40">
-        <v>19.4341650954612</v>
+        <v>15.2771405511666</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>30.14668320805663</v>
+      </c>
+      <c r="C41">
         <v>21.71203386119828</v>
-      </c>
-      <c r="C41">
-        <v>30.14668320805663</v>
       </c>
       <c r="D41">
         <v>4.60574079053509</v>
       </c>
       <c r="E41">
-        <v>14.29752224977414</v>
+        <v>19.85179632085808</v>
       </c>
       <c r="F41">
         <v>65.85068142936778</v>
       </c>
       <c r="G41">
-        <v>19.85179632085808</v>
+        <v>14.29752224977414</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>17.9902873626173</v>
+      </c>
+      <c r="C42">
         <v>23.91280534560193</v>
-      </c>
-      <c r="C42">
-        <v>17.9902873626173</v>
       </c>
       <c r="D42">
         <v>4.181859825927623</v>
       </c>
       <c r="E42">
-        <v>16.85150400123511</v>
+        <v>12.67786840954121</v>
       </c>
       <c r="F42">
         <v>70.47062758922368</v>
       </c>
       <c r="G42">
-        <v>12.67786840954121</v>
+        <v>16.85150400123511</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>29.86225659261798</v>
+      </c>
+      <c r="C43">
         <v>24.66099697949915</v>
-      </c>
-      <c r="C43">
-        <v>29.86225659261798</v>
       </c>
       <c r="D43">
         <v>4.054986101459347</v>
       </c>
       <c r="E43">
-        <v>15.95940831519554</v>
+        <v>19.32541277917181</v>
       </c>
       <c r="F43">
         <v>64.71517890563265</v>
       </c>
       <c r="G43">
-        <v>19.32541277917181</v>
+        <v>15.95940831519554</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>28.73387863354183</v>
+      </c>
+      <c r="C44">
         <v>27.45473108563247</v>
-      </c>
-      <c r="C44">
-        <v>28.73387863354183</v>
       </c>
       <c r="D44">
         <v>3.642359478521052</v>
       </c>
       <c r="E44">
-        <v>17.57793422644316</v>
+        <v>18.39691043105197</v>
       </c>
       <c r="F44">
-        <v>64.02515534250486</v>
+        <v>64.02515534250487</v>
       </c>
       <c r="G44">
-        <v>18.39691043105197</v>
+        <v>17.57793422644317</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>31.62271805273834</v>
+      </c>
+      <c r="C45">
         <v>26.06490872210953</v>
-      </c>
-      <c r="C45">
-        <v>31.62271805273834</v>
       </c>
       <c r="D45">
         <v>3.836575875486381</v>
       </c>
       <c r="E45">
+        <v>20.05402624131721</v>
+      </c>
+      <c r="F45">
+        <v>63.41651659377413</v>
+      </c>
+      <c r="G45">
         <v>16.52945716490867</v>
-      </c>
-      <c r="F45">
-        <v>63.41651659377412</v>
-      </c>
-      <c r="G45">
-        <v>20.05402624131721</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>29.50665031600793</v>
+      </c>
+      <c r="C46">
         <v>29.70002829921706</v>
-      </c>
-      <c r="C46">
-        <v>29.50665031600793</v>
       </c>
       <c r="D46">
         <v>3.367000158805781</v>
       </c>
       <c r="E46">
-        <v>18.65501407198933</v>
+        <v>18.53355058509851</v>
       </c>
       <c r="F46">
         <v>62.81143534291216</v>
       </c>
       <c r="G46">
-        <v>18.53355058509851</v>
+        <v>18.65501407198933</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>29.72466960352423</v>
+      </c>
+      <c r="C47">
         <v>32.00440528634361</v>
-      </c>
-      <c r="C47">
-        <v>29.72466960352423</v>
       </c>
       <c r="D47">
         <v>3.124569855471438</v>
       </c>
       <c r="E47">
+        <v>18.37929860401771</v>
+      </c>
+      <c r="F47">
+        <v>61.83180115764386</v>
+      </c>
+      <c r="G47">
         <v>19.78890023833844</v>
-      </c>
-      <c r="F47">
-        <v>61.83180115764385</v>
-      </c>
-      <c r="G47">
-        <v>18.37929860401771</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>34.70945020543925</v>
+      </c>
+      <c r="C48">
         <v>37.31168068871062</v>
-      </c>
-      <c r="C48">
-        <v>34.70945020543925</v>
       </c>
       <c r="D48">
         <v>2.680125852123755</v>
       </c>
       <c r="E48">
-        <v>21.6901728844404</v>
+        <v>20.17743403093721</v>
       </c>
       <c r="F48">
         <v>58.13239308462239</v>
       </c>
       <c r="G48">
-        <v>20.17743403093721</v>
+        <v>21.6901728844404</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>27.75513581728283</v>
+      </c>
+      <c r="C49">
         <v>25.37600595816869</v>
-      </c>
-      <c r="C49">
-        <v>27.75513581728283</v>
       </c>
       <c r="D49">
         <v>3.940730474482309</v>
       </c>
       <c r="E49">
-        <v>16.57142085140302</v>
+        <v>18.12507599400154</v>
       </c>
       <c r="F49">
         <v>65.30350315459545</v>
       </c>
       <c r="G49">
-        <v>18.12507599400154</v>
+        <v>16.57142085140302</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>30.76535750251762</v>
+      </c>
+      <c r="C50">
         <v>25.92732460557234</v>
-      </c>
-      <c r="C50">
-        <v>30.76535750251762</v>
       </c>
       <c r="D50">
         <v>3.856934779090468</v>
       </c>
       <c r="E50">
-        <v>16.54660846745039</v>
+        <v>19.63420185844737</v>
       </c>
       <c r="F50">
         <v>63.81918967410224</v>
       </c>
       <c r="G50">
-        <v>19.63420185844737</v>
+        <v>16.54660846745039</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>28.71316897173782</v>
+      </c>
+      <c r="C51">
         <v>26.40666609397818</v>
-      </c>
-      <c r="C51">
-        <v>28.71316897173782</v>
       </c>
       <c r="D51">
         <v>3.786922576447625</v>
       </c>
       <c r="E51">
-        <v>17.02339748027136</v>
+        <v>18.51031427384743</v>
       </c>
       <c r="F51">
         <v>64.46628824588122</v>
       </c>
       <c r="G51">
-        <v>18.51031427384743</v>
+        <v>17.02339748027136</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>30.47387554045043</v>
+      </c>
+      <c r="C52">
         <v>21.3598915872572</v>
-      </c>
-      <c r="C52">
-        <v>30.47387554045043</v>
       </c>
       <c r="D52">
         <v>4.681671701913394</v>
       </c>
       <c r="E52">
-        <v>14.06794548494036</v>
+        <v>20.07055223415408</v>
       </c>
       <c r="F52">
         <v>65.86150228090555</v>
       </c>
       <c r="G52">
-        <v>20.07055223415408</v>
+        <v>14.06794548494036</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>28.69927021761384</v>
+      </c>
+      <c r="C53">
         <v>24.9083644288875</v>
-      </c>
-      <c r="C53">
-        <v>28.69927021761384</v>
       </c>
       <c r="D53">
         <v>4.014715630385788</v>
       </c>
       <c r="E53">
-        <v>16.21557710084485</v>
+        <v>18.68349205666745</v>
       </c>
       <c r="F53">
         <v>65.1009308424877</v>
       </c>
       <c r="G53">
-        <v>18.68349205666745</v>
+        <v>16.21557710084485</v>
       </c>
     </row>
   </sheetData>
